--- a/inputs/parameters.xlsx
+++ b/inputs/parameters.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="151">
   <si>
     <t xml:space="preserve">Fichier de paramètre du modèle Quetzal Montréal</t>
   </si>
@@ -280,6 +280,9 @@
     <t xml:space="preserve">futur_express</t>
   </si>
   <si>
+    <t xml:space="preserve">base2</t>
+  </si>
+  <si>
     <t xml:space="preserve">general</t>
   </si>
   <si>
@@ -503,6 +506,9 @@
   </si>
   <si>
     <t xml:space="preserve">route_breaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fast_pt_factor</t>
   </si>
   <si>
     <t xml:space="preserve">logit</t>
@@ -1184,7 +1190,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMJ68"/>
+  <dimension ref="A1:AMJ69"/>
   <sheetFormatPr defaultColWidth="13.171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="26.85"/>
@@ -1193,8 +1199,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="81.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="10" width="17.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="10" width="7.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="12" width="13.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="746" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="12" width="13.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="745" style="0" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" s="13" customFormat="true" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1225,6 +1231,10 @@
       <c r="I1" s="13" t="s">
         <v>30</v>
       </c>
+      <c r="J1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="ALV1" s="0"/>
       <c r="ALW1" s="0"/>
       <c r="ALX1" s="0"/>
       <c r="ALY1" s="0"/>
@@ -1242,13 +1252,13 @@
     </row>
     <row r="2" s="13" customFormat="true" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>28</v>
@@ -1259,6 +1269,10 @@
       <c r="I2" s="13" t="s">
         <v>28</v>
       </c>
+      <c r="J2" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="ALV2" s="0"/>
       <c r="ALW2" s="0"/>
       <c r="ALX2" s="0"/>
       <c r="ALY2" s="0"/>
@@ -1276,95 +1290,103 @@
     </row>
     <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>150</v>
       </c>
       <c r="H3" s="12" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="I3" s="12" t="n">
         <v>150</v>
       </c>
+      <c r="J3" s="12" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="12" t="n">
-        <f aca="false">4/SQRT(2)</f>
-        <v>2.82842712474619</v>
+        <v>1</v>
       </c>
       <c r="I4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="F5" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>1</v>
@@ -1373,19 +1395,22 @@
         <v>1</v>
       </c>
       <c r="I6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>47</v>
-      </c>
       <c r="G7" s="12" t="n">
         <v>1</v>
       </c>
@@ -1393,21 +1418,24 @@
         <v>1</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>1</v>
@@ -1416,21 +1444,24 @@
         <v>1</v>
       </c>
       <c r="I8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" s="17" t="n">
         <f aca="false">FALSE()</f>
@@ -1444,22 +1475,26 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="J9" s="17" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>100</v>
@@ -1470,19 +1505,22 @@
       <c r="I10" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="J10" s="12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>500</v>
@@ -1493,19 +1531,22 @@
       <c r="I11" s="12" t="n">
         <v>500</v>
       </c>
+      <c r="J11" s="12" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>4</v>
@@ -1516,43 +1557,48 @@
       <c r="I12" s="12" t="n">
         <v>4</v>
       </c>
+      <c r="J12" s="12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H13" s="12" t="n">
-        <f aca="false">4/SQRT(2)</f>
-        <v>2.82842712474619</v>
+        <v>10</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="J13" s="12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>10000000</v>
@@ -1563,19 +1609,22 @@
       <c r="I14" s="12" t="n">
         <v>10000000</v>
       </c>
+      <c r="J14" s="12" t="n">
+        <v>10000000</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>10</v>
@@ -1586,19 +1635,22 @@
       <c r="I15" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="J15" s="12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G16" s="12" t="n">
         <f aca="false">30</f>
@@ -1612,19 +1664,23 @@
         <f aca="false">30</f>
         <v>30</v>
       </c>
+      <c r="J16" s="12" t="n">
+        <f aca="false">30</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
@@ -1633,21 +1689,24 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0.5</v>
@@ -1658,19 +1717,22 @@
       <c r="I18" s="12" t="n">
         <v>0.5</v>
       </c>
+      <c r="J18" s="12" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>1.5</v>
@@ -1681,19 +1743,22 @@
       <c r="I19" s="12" t="n">
         <v>1.5</v>
       </c>
+      <c r="J19" s="12" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>74</v>
-      </c>
       <c r="F20" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0.5</v>
@@ -1704,19 +1769,22 @@
       <c r="I20" s="12" t="n">
         <v>0.5</v>
       </c>
+      <c r="J20" s="12" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>1.5</v>
@@ -1727,19 +1795,22 @@
       <c r="I21" s="12" t="n">
         <v>1.5</v>
       </c>
+      <c r="J21" s="12" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0.5</v>
@@ -1750,19 +1821,22 @@
       <c r="I22" s="12" t="n">
         <v>0.5</v>
       </c>
+      <c r="J22" s="12" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>1</v>
@@ -1771,18 +1845,21 @@
         <v>1</v>
       </c>
       <c r="I23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G24" s="17" t="n">
         <f aca="false">FALSE()</f>
@@ -1796,19 +1873,23 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="J24" s="17" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>0</v>
@@ -1817,18 +1898,21 @@
         <v>0</v>
       </c>
       <c r="I25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0</v>
@@ -1837,21 +1921,24 @@
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>0</v>
@@ -1860,18 +1947,21 @@
         <v>0</v>
       </c>
       <c r="I27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F28" s="10" t="n">
         <v>0</v>
@@ -1883,18 +1973,21 @@
         <v>1</v>
       </c>
       <c r="I28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>0</v>
@@ -1906,18 +1999,21 @@
         <v>1</v>
       </c>
       <c r="I29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>1</v>
@@ -1931,16 +2027,19 @@
       <c r="I30" s="12" t="n">
         <v>0.01</v>
       </c>
+      <c r="J30" s="12" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>1</v>
@@ -1954,88 +2053,100 @@
       <c r="I31" s="12" t="n">
         <v>0.01</v>
       </c>
+      <c r="J31" s="12" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>1000</v>
       </c>
+      <c r="J32" s="12" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B33" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="F33" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>1000</v>
       </c>
+      <c r="J33" s="12" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>50000</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>10800</v>
+        <v>50000</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>50000</v>
       </c>
+      <c r="J34" s="12" t="n">
+        <v>50000</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>1</v>
@@ -2044,18 +2155,21 @@
         <v>1</v>
       </c>
       <c r="I35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>1</v>
@@ -2064,75 +2178,87 @@
         <v>1</v>
       </c>
       <c r="I36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="10" t="s">
-        <v>110</v>
+      <c r="F38" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.00032</v>
+        <v>0</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0.00032</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.00032</v>
+        <v>0</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B39" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="E39" s="10" t="s">
         <v>112</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.6</v>
+        <v>0.00032</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>1.6</v>
+        <v>0.00032</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>1.6</v>
+        <v>0.00032</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>0.00032</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>113</v>
@@ -2141,88 +2267,97 @@
         <v>114</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D41" s="10"/>
-      <c r="F41" s="10" t="s">
-        <v>38</v>
+      <c r="D41" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" s="10" t="s">
         <v>117</v>
       </c>
+      <c r="D42" s="10"/>
       <c r="F42" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="D43" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D43" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>121</v>
+      <c r="F43" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>122</v>
@@ -2231,38 +2366,47 @@
         <v>123</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B45" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="E45" s="10" t="s">
         <v>125</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>126</v>
@@ -2271,18 +2415,21 @@
         <v>127</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="J46" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>128</v>
@@ -2291,18 +2438,21 @@
         <v>129</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="J47" s="12" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>130</v>
@@ -2310,173 +2460,190 @@
       <c r="D48" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="G48" s="12" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>10</v>
+        <v>0.1</v>
+      </c>
+      <c r="J48" s="12" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B49" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="E49" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>38</v>
-      </c>
       <c r="G49" s="12" t="n">
-        <v>1800</v>
+        <v>1</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>2700</v>
+        <v>1</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>135</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>100</v>
+        <v>500</v>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B51" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>134</v>
-      </c>
       <c r="F51" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D52" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G52" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B53" s="24" t="s">
+      <c r="B53" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="D53" s="25" t="s">
+      <c r="D53" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="G53" s="26" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H53" s="26" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I53" s="26" t="n">
-        <v>-2</v>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B54" s="24" t="s">
         <v>142</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E54" s="23"/>
       <c r="F54" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G54" s="26" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H54" s="26" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I54" s="26" t="n">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J54" s="26" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B55" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D55" s="25" t="s">
         <v>143</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>141</v>
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G55" s="26" t="n">
         <v>0</v>
@@ -2485,22 +2652,25 @@
         <v>0</v>
       </c>
       <c r="I55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E56" s="23"/>
       <c r="F56" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G56" s="26" t="n">
         <v>0</v>
@@ -2509,22 +2679,25 @@
         <v>0</v>
       </c>
       <c r="I56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E57" s="23"/>
       <c r="F57" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G57" s="26" t="n">
         <v>0</v>
@@ -2533,22 +2706,25 @@
         <v>0</v>
       </c>
       <c r="I57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E58" s="23"/>
       <c r="F58" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G58" s="26" t="n">
         <v>0</v>
@@ -2557,22 +2733,25 @@
         <v>0</v>
       </c>
       <c r="I58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E59" s="23"/>
       <c r="F59" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G59" s="26" t="n">
         <v>0</v>
@@ -2583,92 +2762,104 @@
       <c r="I59" s="26" t="n">
         <v>0</v>
       </c>
+      <c r="J59" s="26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="D60" s="21" t="s">
+      <c r="A60" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G60" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="22" t="n">
+      <c r="B60" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B61" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="D61" s="25" t="s">
+      <c r="D61" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="G61" s="26" t="n">
-        <v>-600</v>
-      </c>
-      <c r="H61" s="26" t="n">
-        <v>-600</v>
-      </c>
-      <c r="I61" s="26" t="n">
-        <v>-600</v>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B62" s="24" t="s">
         <v>142</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E62" s="23"/>
       <c r="F62" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G62" s="26" t="n">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="H62" s="26" t="n">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="I62" s="26" t="n">
-        <v>0</v>
+        <v>-600</v>
+      </c>
+      <c r="J62" s="26" t="n">
+        <v>-600</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B63" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D63" s="25" t="s">
         <v>143</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>141</v>
       </c>
       <c r="E63" s="23"/>
       <c r="F63" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G63" s="26" t="n">
         <v>0</v>
@@ -2677,47 +2868,52 @@
         <v>0</v>
       </c>
       <c r="I63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E64" s="23"/>
       <c r="F64" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G64" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="26" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" s="27"/>
+        <v>146</v>
+      </c>
       <c r="D65" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E65" s="23"/>
       <c r="F65" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G65" s="26" t="n">
         <v>0</v>
@@ -2726,23 +2922,26 @@
         <v>0</v>
       </c>
       <c r="I65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C66" s="27"/>
       <c r="D66" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E66" s="23"/>
       <c r="F66" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G66" s="26" t="n">
         <v>0</v>
@@ -2751,22 +2950,26 @@
         <v>0</v>
       </c>
       <c r="I66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="10" t="s">
-        <v>147</v>
-      </c>
+      <c r="C67" s="27"/>
       <c r="D67" s="25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E67" s="23"/>
       <c r="F67" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G67" s="26" t="n">
         <v>0</v>
@@ -2777,17 +2980,48 @@
       <c r="I67" s="26" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0"/>
-      <c r="B68" s="0"/>
-      <c r="C68" s="0"/>
-      <c r="D68" s="0"/>
-      <c r="E68" s="0"/>
-      <c r="F68" s="0"/>
-      <c r="G68" s="0"/>
-      <c r="H68" s="0"/>
-      <c r="I68" s="0"/>
+      <c r="J67" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D68" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E68" s="23"/>
+      <c r="F68" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0"/>
+      <c r="B69" s="0"/>
+      <c r="C69" s="0"/>
+      <c r="D69" s="0"/>
+      <c r="E69" s="0"/>
+      <c r="F69" s="0"/>
+      <c r="G69" s="0"/>
+      <c r="H69" s="0"/>
+      <c r="I69" s="0"/>
+      <c r="J69" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
